--- a/results/job_matches_2026-09-26.xlsx
+++ b/results/job_matches_2026-09-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer</t>
+          <t>Senior Python Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Everon</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bf341f814fc4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=dac7d146ce85fb43</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect</t>
+          <t>Software Engineer lll - Senior Databricks/Spark/AWS Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=536f7d54c3314639</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a9159a42796f24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, PySpark, AWS)</t>
+          <t>Senior Data Integration Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Everon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec4e00003379849</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bf341f814fc4d9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Enterprise Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Data Modeling, ELT, MLflow</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a436017e20a9af4</t>
+          <t>https://www.indeed.com/viewjob?jk=536f7d54c3314639</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Systems Engineer (TraCSS Mission Integration)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>ASRC Federal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Suitland-Silver Hill, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5929a259b13da0</t>
+          <t>https://www.indeed.com/viewjob?jk=4229e45505a54081</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Intern, IT Data Analytics (2027)</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hollister Incorporated</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f2045b50523bff</t>
+          <t>https://www.indeed.com/viewjob?jk=ed5929a259b13da0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Intern, IT Data Analytics (2027)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hollister Incorporated</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea69319765aa1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f2045b50523bff</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Architect / Engineer</t>
+          <t>Software Engineer-Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa811352fa1aa90</t>
+          <t>https://www.indeed.com/viewjob?jk=96d6f3a23638523d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer-Remote</t>
+          <t>Sr Data Engineer, AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, GCP, Spark, PySpark, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96d6f3a23638523d</t>
+          <t>https://www.indeed.com/viewjob?jk=05fc81fdc3c7e4c8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PRADCO</t>
+          <t>Bronco Wine Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Ceres, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Star Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9009df35d7b57b</t>
+          <t>https://www.indeed.com/viewjob?jk=5e558da34cfe637e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>DevSecOps</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Steerbridge</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Azure, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de31c40d2a0ecf08</t>
+          <t>https://www.indeed.com/viewjob?jk=c41e154e6981a638</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DWBI Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>Jersey Mike's</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ad36cd86055a44</t>
+          <t>https://www.indeed.com/viewjob?jk=03f2e368fab4382a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224df3f1a9ee79b8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef89900c1dc8244</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7055be6d8f9a7387</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ad36cd86055a44</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d8c98cbbde5e5</t>
+          <t>https://www.indeed.com/viewjob?jk=224df3f1a9ee79b8</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf28aa480065b669</t>
+          <t>https://www.indeed.com/viewjob?jk=7055be6d8f9a7387</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944cc70dff5af5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d8c98cbbde5e5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b557a1c3d0e30a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf28aa480065b669</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221dce02ae4400cf</t>
+          <t>https://www.indeed.com/viewjob?jk=944cc70dff5af5ad</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data &amp; AI Intern</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47848c785f526698</t>
+          <t>https://www.indeed.com/viewjob?jk=aa6bfaadd5a59007</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Full Stack Developer (Internal Tools &amp; Platform)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Magnaflow</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oceanside, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
+          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6729a082d816c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0c40611e6f1095</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Internal Tools &amp; Platform)</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0c40611e6f1095</t>
+          <t>https://www.indeed.com/viewjob?jk=b557a1c3d0e30a4a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AFTERWORK</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>London, OH, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462d1dfaba6a7d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=221dce02ae4400cf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Frontend Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>AFTERWORK</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>London, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa90431a3fa096c</t>
+          <t>https://www.indeed.com/viewjob?jk=462d1dfaba6a7d7d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TWFG Insurance</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Dataflow, Spark, PySpark, Scala, Fact Tables</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc6da2f4c063d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa90431a3fa096c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Data Engineer, AI Data Products</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lincoln Financial</t>
+          <t>TWFG Insurance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, Spark, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Dataflow, Spark, PySpark, Scala, Fact Tables</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326243a7df349c66</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc6da2f4c063d5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Associate Data Engineer, AI Data Products</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, Spark, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be84cd3bc47c5004</t>
+          <t>https://www.indeed.com/viewjob?jk=326243a7df349c66</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Financial Systems (Remote)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4cee9cb47e0f3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=be84cd3bc47c5004</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998cfb2b283317ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6f816dbfdf0d99a1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Connected Vehicle &amp; Telematics (GCP)</t>
+          <t>Sr. Data Engineer, Financial Systems (Remote)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, PostgreSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc0d2abdbe910d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4cee9cb47e0f3e3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Tableau, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5662b2a7e9c297d</t>
+          <t>https://www.indeed.com/viewjob?jk=998cfb2b283317ea</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Backend Engineer, Connected Vehicle &amp; Telematics (GCP)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, PostgreSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5d06d511ed0f968</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc0d2abdbe910d6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML Infrastructure</t>
+          <t>Data Engineer II (School of Medicine)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae962c4658819a4</t>
+          <t>https://www.indeed.com/viewjob?jk=379a8ad8bec448ca</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6054cc97ae7070</t>
+          <t>https://www.indeed.com/viewjob?jk=d5d06d511ed0f968</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131728c21bda1a28</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae962c4658819a4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jobs for you</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15797458cef00167</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6054cc97ae7070</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ae0bf58018f888</t>
+          <t>https://www.indeed.com/viewjob?jk=131728c21bda1a28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Jobs for you</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dce389fccfb3534</t>
+          <t>https://www.indeed.com/viewjob?jk=15797458cef00167</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, ETL, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57742a64192a9c15</t>
+          <t>https://www.indeed.com/viewjob?jk=42e2ea145c1d3563</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VMware VDI to AWS WorkSpaces Core Migration Architect</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bd9b74a1882f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=49d99cd342cc792a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Analytics Analyst</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=945bd3fa6f051f40</t>
+          <t>https://www.indeed.com/viewjob?jk=8b8cf7db016ac733</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Information Technology Architect | (Cloud Engineer)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>City of Atlanta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e657852ef5f740</t>
+          <t>https://www.indeed.com/viewjob?jk=b342fa1c8138648d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineering Associate</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45ecb961e115a14</t>
+          <t>https://www.indeed.com/viewjob?jk=f78903bdefa25d5d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902a69e0fc5e870</t>
+          <t>https://www.indeed.com/viewjob?jk=72c9885d1791465d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Scala, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac2005fd12c4ec8</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3e09f803e1046e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Scala, NoSQL, Data Modeling, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52509eca710cb0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5b8f3fa6f2af02</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07bb0961c751f3e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ae0bf58018f888</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Distinguished AI and Data Security Engineer</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d3211f519b547f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7dce389fccfb3534</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Senior Engineer, Customer Store Experience</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f2dbc076e5d856</t>
+          <t>https://www.indeed.com/viewjob?jk=bab9f52b7b9fec24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>VMware VDI to AWS WorkSpaces Core Migration Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6929f0e8b0d467e</t>
+          <t>https://www.indeed.com/viewjob?jk=78bd9b74a1882f4e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Information Technology Architect | (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>City of Atlanta</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55bf5e8aa6a1b00</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e657852ef5f740</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Sr. Analytics Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b85bc0bda01150</t>
+          <t>https://www.indeed.com/viewjob?jk=945bd3fa6f051f40</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Data Engineering Associate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a187bc45f903c25</t>
+          <t>https://www.indeed.com/viewjob?jk=a45ecb961e115a14</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Java/Spring Boot Software Engineer/Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Aguadilla, PR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ea3b4e869f0b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9abe3f58667967b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Hive, Spark, Scala, NoSQL, Data Modeling, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c766c5fed70eb0a</t>
+          <t>https://www.indeed.com/viewjob?jk=52509eca710cb0dc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bcda2cd30fd616</t>
+          <t>https://www.indeed.com/viewjob?jk=c07bb0961c751f3e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Distinguished AI and Data Security Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638ef8567418dc48</t>
+          <t>https://www.indeed.com/viewjob?jk=8d3211f519b547f7</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1a136d608291b</t>
+          <t>https://www.indeed.com/viewjob?jk=99f2dbc076e5d856</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd00710707d78e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a6929f0e8b0d467e</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442e1899472aaaca</t>
+          <t>https://www.indeed.com/viewjob?jk=b55bf5e8aa6a1b00</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17caa029de510739</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b85bc0bda01150</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42aa0c7cd36d006a</t>
+          <t>https://www.indeed.com/viewjob?jk=9a187bc45f903c25</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab6925d775e203f</t>
+          <t>https://www.indeed.com/viewjob?jk=19ea3b4e869f0b0f</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5653e98fb8135f3</t>
+          <t>https://www.indeed.com/viewjob?jk=9c766c5fed70eb0a</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=687232035e68a0a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bcda2cd30fd616</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ba9f5f8c57b5360</t>
+          <t>https://www.indeed.com/viewjob?jk=638ef8567418dc48</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7126e5851d589397</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1a136d608291b</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77cfd4f7c6e8001</t>
+          <t>https://www.indeed.com/viewjob?jk=edd00710707d78e9</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59304446412e07c</t>
+          <t>https://www.indeed.com/viewjob?jk=442e1899472aaaca</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b64c007a0de94064</t>
+          <t>https://www.indeed.com/viewjob?jk=17caa029de510739</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86388f3c259eeff8</t>
+          <t>https://www.indeed.com/viewjob?jk=42aa0c7cd36d006a</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675f32b4ffa9a13</t>
+          <t>https://www.indeed.com/viewjob?jk=cab6925d775e203f</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034638488092da65</t>
+          <t>https://www.indeed.com/viewjob?jk=d5653e98fb8135f3</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac28966ddf697160</t>
+          <t>https://www.indeed.com/viewjob?jk=687232035e68a0a9</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24729823d8955c30</t>
+          <t>https://www.indeed.com/viewjob?jk=8ba9f5f8c57b5360</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87a502c5ba52e486</t>
+          <t>https://www.indeed.com/viewjob?jk=7126e5851d589397</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a20461db3b55f8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a77cfd4f7c6e8001</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c63497e49a35949</t>
+          <t>https://www.indeed.com/viewjob?jk=f59304446412e07c</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6deed82147b3397a</t>
+          <t>https://www.indeed.com/viewjob?jk=b64c007a0de94064</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ab915125e1142b</t>
+          <t>https://www.indeed.com/viewjob?jk=86388f3c259eeff8</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e19c0167b5b707</t>
+          <t>https://www.indeed.com/viewjob?jk=9675f32b4ffa9a13</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3957c8134eb5449d</t>
+          <t>https://www.indeed.com/viewjob?jk=034638488092da65</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131fbd30ebce4b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac28966ddf697160</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc69f1717479209</t>
+          <t>https://www.indeed.com/viewjob?jk=24729823d8955c30</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbd490415ec98b8</t>
+          <t>https://www.indeed.com/viewjob?jk=87a502c5ba52e486</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9da7e405560c98</t>
+          <t>https://www.indeed.com/viewjob?jk=a20461db3b55f8e5</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d443ab17a64dc4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=3c63497e49a35949</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe9a8ea39da933e</t>
+          <t>https://www.indeed.com/viewjob?jk=6deed82147b3397a</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2436088e04cb9418</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ab915125e1142b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4760b3a15e7c28bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e19c0167b5b707</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a34bf218fa3ecdb</t>
+          <t>https://www.indeed.com/viewjob?jk=3957c8134eb5449d</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c29c8279e212129</t>
+          <t>https://www.indeed.com/viewjob?jk=131fbd30ebce4b0e</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbc6b68160b7f80</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc69f1717479209</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67361e9400bbca3</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbd490415ec98b8</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56277a5a14ecfae3</t>
+          <t>https://www.indeed.com/viewjob?jk=de9da7e405560c98</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64341d28e22d4d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=d443ab17a64dc4a2</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0db3535ef241d9</t>
+          <t>https://www.indeed.com/viewjob?jk=abe9a8ea39da933e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Full Stack and Cloud Platform Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ecebecfe672f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=2436088e04cb9418</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer (175879)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c9cd63529737fa</t>
+          <t>https://www.indeed.com/viewjob?jk=4760b3a15e7c28bf</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Architect</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KNS IT Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, DataOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55665d3cb959d92b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a34bf218fa3ecdb</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,67 +4101,67 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eff740f1ceace8</t>
+          <t>https://www.indeed.com/viewjob?jk=4c29c8279e212129</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MicroStrategy Developer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, MicroStrategy, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb797238596b5283</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbc6b68160b7f80</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Kiewit Technology Group</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69fd302298183375</t>
+          <t>https://www.indeed.com/viewjob?jk=e67361e9400bbca3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sentara</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0364757c79beba</t>
+          <t>https://www.indeed.com/viewjob?jk=56277a5a14ecfae3</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d893afa2af62f4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=64341d28e22d4d4a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1919471b72d0ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0db3535ef241d9</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack and Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,54 +4311,54 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695ee016a6862deb</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ecebecfe672f7c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (175879)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74dc88aa87ede3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=20c9cd63529737fa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS DevOps Architect</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ezee Fiber</t>
+          <t>KNS IT Group</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4367,33 +4367,33 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, PostgreSQL, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, Scala, DataOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14553b87b9e8856d</t>
+          <t>https://www.indeed.com/viewjob?jk=55665d3cb959d92b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Associate Actuary II</t>
+          <t>Senior Software Engineer (Platform Engineering)-Remote, USA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4402,11 +4402,11 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, MySQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfc7194d4a210ff</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ab6a43be12efda</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Associate Data Engineer, AI Data Products</t>
+          <t>Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lincoln Financial</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, API Gateway, ECS, IAM, RDS, dbt, MLOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63821a0502f55779</t>
+          <t>https://www.indeed.com/viewjob?jk=85eff740f1ceace8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Power BI)</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d65655a9bdf8af8</t>
+          <t>https://www.indeed.com/viewjob?jk=a07d991630064dac</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Solutions Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddff3d8fcac07d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=a46b634577cae67c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Matterport</t>
+          <t>Software Engineer 1 - Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbdfdc99e931506</t>
+          <t>https://www.indeed.com/viewjob?jk=69fd302298183375</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II - REMOTE</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Sentara</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13861c16b28c1ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0364757c79beba</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>iDC Logistics</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f033dfebaee3ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d893afa2af62f4a2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer 1 4P/846</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Forest Park, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c5956a500a065e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1919471b72d0ae9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ezee Fiber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Wausau, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, PostgreSQL, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8593692b74910cb</t>
+          <t>https://www.indeed.com/viewjob?jk=14553b87b9e8856d</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Associate Data Engineer, AI Data Products</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, API Gateway, ECS, IAM, RDS, dbt, MLOps</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc24126bb01a3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=63821a0502f55779</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DevSecOps Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>iDC Logistics</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,19 +4766,19 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21206c796173cd36</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f033dfebaee3ca</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Associate Actuary II</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4787,11 +4787,11 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ecde40997dfe59</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfc7194d4a210ff</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+          <t>Business Intelligence Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2b3596f51501b1</t>
+          <t>https://www.indeed.com/viewjob?jk=13861c16b28c1ecd</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wausau, WI, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70480a7733a24dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=b8593692b74910cb</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer - Python ,AWS, SQL - Remote</t>
+          <t>Senior DevOps Engineer - Matterport</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfefbbb5df74fffe</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbdfdc99e931506</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (AI / ML) - Spring 2027</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,59 +4941,59 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefb70733fd4805b</t>
+          <t>https://www.indeed.com/viewjob?jk=ddff3d8fcac07d3a</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 - Payment Network Partner Experience</t>
+          <t>Analytics Engineer (Power BI)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e45723ef8f4f70</t>
+          <t>https://www.indeed.com/viewjob?jk=6d65655a9bdf8af8</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud BigData Engineer</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ab60d145780389</t>
+          <t>https://www.indeed.com/viewjob?jk=38ecde40997dfe59</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa8366af2ac5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=7f2b3596f51501b1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. Data and Platform Engineer</t>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, PySpark, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b516dee5bebdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=70480a7733a24dbb</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer - EDW Team</t>
+          <t>Data Engineer - Python ,AWS, SQL - Remote</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>G.E.H.A</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lee's Summit, MO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda83b90519c1a63</t>
+          <t>https://www.indeed.com/viewjob?jk=bfefbbb5df74fffe</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AI Data Engineer Intern - QuantumBlack, AI by McKinsey</t>
+          <t>Agentic Data Engineer, IC2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>ClassLink, Inc.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt, Git, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1697413820124a26</t>
+          <t>https://www.indeed.com/viewjob?jk=2a242ddcff013ad3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fad152308282f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c121478651fef59</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7239eb247bd719da</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa8366af2ac5a61</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data and Platform Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, PySpark, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdece1225c2c990</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b516dee5bebdf7</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Cloud Data Engineer - EDW Team</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>G.E.H.A</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Lee's Summit, MO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858fa984b328a939</t>
+          <t>https://www.indeed.com/viewjob?jk=eda83b90519c1a63</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer IV – Claims</t>
+          <t>AI Data Engineer Intern - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91758534ce0e5b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=1697413820124a26</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr Developer, Enterprise Applications</t>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7df0d2f19226e92</t>
+          <t>https://www.indeed.com/viewjob?jk=29fad152308282f5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr Developer, Enterprise Applications</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cfdfcbeb6f3aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdece1225c2c990</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr Functional Analyst with Data Connect / Integration</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd158f889951e37</t>
+          <t>https://www.indeed.com/viewjob?jk=858fa984b328a939</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack</t>
+          <t>Cloud Software Engineer (Azure)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, GCP, Snowflake, dbt, CI/CD, GitHub Actions, Docker</t>
+          <t>Azure, Data Factory, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00f231ced225306d</t>
+          <t>https://www.indeed.com/viewjob?jk=67e15f97e5cb54f7</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,17 +5491,367 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Power BI, Tableau, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d98d3b46d4d0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=02f995067a8af808</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>DevOps Engineer, Level 3</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>FJA-US Inc.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad4efa0feb82038a</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>DevOps Engineer, Level 3</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>FJA-US Inc.</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68a87d8ccc941480</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior Applications &amp; Data Analyst</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>The Community Foundation for Greater Atlanta</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Cloud Storage, Scala, Power BI, Tableau, AKS</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67c100e86a4b30b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Sr Developer, Enterprise Applications</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Pilot Flying J</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Orange, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7df0d2f19226e92</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Sr Developer, Enterprise Applications</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Pilot Flying J</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9cfdfcbeb6f3aa6</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Sr Functional Analyst with Data Connect / Integration</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afd158f889951e37</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Software Application Developer, IV IT</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Centurion Health</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a31f79172dd2cf72</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer IV – Claims</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>The Standard Insurance</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91758534ce0e5b1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Software Engineer, Full Stack</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Athena, RDS, GCP, Snowflake, dbt, CI/CD, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00f231ced225306d</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Kafka, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73912ee7f3217027</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-26.xlsx
+++ b/results/job_matches_2026-09-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Full-stack Engineer 4 (Apache Spark and Java)( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5929a259b13da0</t>
+          <t>https://www.indeed.com/viewjob?jk=1c536a9bd99ef94e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Intern, IT Data Analytics (2027)</t>
+          <t>Full-stack Engineer 4 (Apache Spark and Java)( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hollister Incorporated</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f2045b50523bff</t>
+          <t>https://www.indeed.com/viewjob?jk=61acd17e8e4caf4c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data - Medical Cost Grouper - Remote</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, HBase, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ee7d4f1fc05ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=ed5929a259b13da0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer-Remote</t>
+          <t>Intern, IT Data Analytics (2027)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Hollister Incorporated</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96d6f3a23638523d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f2045b50523bff</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, AI</t>
+          <t>Senior Engineer, Big Data - Medical Cost Grouper - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, GCP, Spark, PySpark, SQL Server</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, HBase, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05fc81fdc3c7e4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=10ee7d4f1fc05ba7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Sr Data Engineer, AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bronco Wine Company</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ceres, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Star Schema, Fact Tables</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, GCP, Spark, PySpark, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e558da34cfe637e</t>
+          <t>https://www.indeed.com/viewjob?jk=05fc81fdc3c7e4c8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevSecOps</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Steerbridge</t>
+          <t>Bronco Wine Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Ceres, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Azure, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Star Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c41e154e6981a638</t>
+          <t>https://www.indeed.com/viewjob?jk=5e558da34cfe637e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DWBI Architect</t>
+          <t>DevSecOps</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jersey Mike's</t>
+          <t>Steerbridge</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Azure, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f2e368fab4382a</t>
+          <t>https://www.indeed.com/viewjob?jk=c41e154e6981a638</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DWBI Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Jersey Mike's</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef89900c1dc8244</t>
+          <t>https://www.indeed.com/viewjob?jk=03f2e368fab4382a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Software Engineer, Integrity</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ad36cd86055a44</t>
+          <t>https://www.indeed.com/viewjob?jk=836233526c2bfe4c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224df3f1a9ee79b8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef89900c1dc8244</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer, Integrity</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Dimensional Modeling, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7055be6d8f9a7387</t>
+          <t>https://www.indeed.com/viewjob?jk=986e0cd967904817</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d8c98cbbde5e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ad36cd86055a44</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf28aa480065b669</t>
+          <t>https://www.indeed.com/viewjob?jk=224df3f1a9ee79b8</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944cc70dff5af5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7055be6d8f9a7387</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa6bfaadd5a59007</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d8c98cbbde5e5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Internal Tools &amp; Platform)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0c40611e6f1095</t>
+          <t>https://www.indeed.com/viewjob?jk=cf28aa480065b669</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b557a1c3d0e30a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=944cc70dff5af5ad</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221dce02ae4400cf</t>
+          <t>https://www.indeed.com/viewjob?jk=aa6bfaadd5a59007</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>Full Stack Developer (Internal Tools &amp; Platform)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AFTERWORK</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>London, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462d1dfaba6a7d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0c40611e6f1095</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa90431a3fa096c</t>
+          <t>https://www.indeed.com/viewjob?jk=b557a1c3d0e30a4a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TWFG Insurance</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Dataflow, Spark, PySpark, Scala, Fact Tables</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc6da2f4c063d5</t>
+          <t>https://www.indeed.com/viewjob?jk=221dce02ae4400cf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Data Engineer, AI Data Products</t>
+          <t>Frontend Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lincoln Financial</t>
+          <t>AFTERWORK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>London, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, Spark, Data Modeling, dbt</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326243a7df349c66</t>
+          <t>https://www.indeed.com/viewjob?jk=462d1dfaba6a7d7d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Site Reliability Engineer, Data - FreeWheel</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be84cd3bc47c5004</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2dcbf84370ecd2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AWS Cloud</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>TWFG Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Dataflow, Spark, PySpark, Scala, Fact Tables</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f816dbfdf0d99a1</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc6da2f4c063d5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Financial Systems (Remote)</t>
+          <t>Associate Data Engineer, AI Data Products</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, Spark, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4cee9cb47e0f3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=326243a7df349c66</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998cfb2b283317ea</t>
+          <t>https://www.indeed.com/viewjob?jk=be84cd3bc47c5004</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Connected Vehicle &amp; Telematics (GCP)</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, PostgreSQL, MLOps, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc0d2abdbe910d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6f816dbfdf0d99a1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II (School of Medicine)</t>
+          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a8ad8bec448ca</t>
+          <t>https://www.indeed.com/viewjob?jk=998cfb2b283317ea</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer II (School of Medicine)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5d06d511ed0f968</t>
+          <t>https://www.indeed.com/viewjob?jk=379a8ad8bec448ca</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML Infrastructure</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae962c4658819a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5d06d511ed0f968</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>DevOps Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6054cc97ae7070</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae962c4658819a4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131728c21bda1a28</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6054cc97ae7070</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jobs for you</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15797458cef00167</t>
+          <t>https://www.indeed.com/viewjob?jk=131728c21bda1a28</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Analytics Analyst</t>
+          <t>Data Engineering Associate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=945bd3fa6f051f40</t>
+          <t>https://www.indeed.com/viewjob?jk=a45ecb961e115a14</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineering Associate</t>
+          <t>Sr. Analytics Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45ecb961e115a14</t>
+          <t>https://www.indeed.com/viewjob?jk=945bd3fa6f051f40</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Full Stack and Cloud Platform Engineer</t>
+          <t>Senior Software Engineer (Platform Engineering)-Remote, USA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, MySQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ecebecfe672f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ab6a43be12efda</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer (175879)</t>
+          <t>Senior AWS DevOps Architect</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>KNS IT Group</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, DataOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c9cd63529737fa</t>
+          <t>https://www.indeed.com/viewjob?jk=55665d3cb959d92b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Architect</t>
+          <t>Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KNS IT Group</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, DataOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55665d3cb959d92b</t>
+          <t>https://www.indeed.com/viewjob?jk=85eff740f1ceace8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Engineering)-Remote, USA</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ab6a43be12efda</t>
+          <t>https://www.indeed.com/viewjob?jk=a07d991630064dac</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid</t>
+          <t>Cloud Data Solutions Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, DynamoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eff740f1ceace8</t>
+          <t>https://www.indeed.com/viewjob?jk=a46b634577cae67c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Software Engineer 1 - Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07d991630064dac</t>
+          <t>https://www.indeed.com/viewjob?jk=69fd302298183375</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer - Financial Services</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sentara</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46b634577cae67c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0364757c79beba</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Kiewit Technology Group</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69fd302298183375</t>
+          <t>https://www.indeed.com/viewjob?jk=d893afa2af62f4a2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Sentara</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0364757c79beba</t>
+          <t>https://www.indeed.com/viewjob?jk=e1919471b72d0ae9</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Ezee Fiber</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, PostgreSQL, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d893afa2af62f4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=14553b87b9e8856d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Associate Actuary II</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1919471b72d0ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfc7194d4a210ff</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ezee Fiber</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, PostgreSQL, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14553b87b9e8856d</t>
+          <t>https://www.indeed.com/viewjob?jk=13861c16b28c1ecd</t>
         </is>
       </c>
     </row>
@@ -4773,17 +4773,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Associate Actuary II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wausau, WI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfc7194d4a210ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b8593692b74910cb</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II - REMOTE</t>
+          <t>Senior DevOps Engineer - Matterport</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13861c16b28c1ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbdfdc99e931506</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wausau, WI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8593692b74910cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ddff3d8fcac07d3a</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Matterport</t>
+          <t>Full-stack Engineer 5 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbdfdc99e931506</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e33ea940cfabaf</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddff3d8fcac07d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c52f54f8e5be210c</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Power BI)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d65655a9bdf8af8</t>
+          <t>https://www.indeed.com/viewjob?jk=bca244a4074f26cb</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Full Stack Engineer - 4</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,14 +5011,14 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ecde40997dfe59</t>
+          <t>https://www.indeed.com/viewjob?jk=4acbff2d0e6ba792</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -5046,14 +5046,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2b3596f51501b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a726f18ef6bec68d</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5063,11 +5063,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70480a7733a24dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=9360083577d366e1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Engineer - Python ,AWS, SQL - Remote</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfefbbb5df74fffe</t>
+          <t>https://www.indeed.com/viewjob?jk=26af012597a937ac</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Agentic Data Engineer, IC2</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS, API, UI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ClassLink, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a242ddcff013ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=0a471487d6e7ce5e</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer 4 (Bank Tech)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c121478651fef59</t>
+          <t>https://www.indeed.com/viewjob?jk=206971bfe0c7648e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa8366af2ac5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=f700dc035e701b44</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr. Data and Platform Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, PySpark, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b516dee5bebdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=cbde946ea5f19114</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer - EDW Team</t>
+          <t>Full-stack Engineer 4 (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>G.E.H.A</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Lee's Summit, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda83b90519c1a63</t>
+          <t>https://www.indeed.com/viewjob?jk=3f21d9e3e95a919b</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AI Data Engineer Intern - QuantumBlack, AI by McKinsey</t>
+          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1697413820124a26</t>
+          <t>https://www.indeed.com/viewjob?jk=befbf1e1c644225d</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+          <t>Analytics Engineer (Power BI)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fad152308282f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6d65655a9bdf8af8</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdece1225c2c990</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc7880b49c1e317</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858fa984b328a939</t>
+          <t>https://www.indeed.com/viewjob?jk=38ecde40997dfe59</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer (Azure)</t>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67e15f97e5cb54f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f2b3596f51501b1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Level 3</t>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FJA-US Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f995067a8af808</t>
+          <t>https://www.indeed.com/viewjob?jk=70480a7733a24dbb</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Level 3</t>
+          <t>Agentic Data Engineer, IC2</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FJA-US Inc.</t>
+          <t>ClassLink, Inc.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4efa0feb82038a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a242ddcff013ad3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Level 3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FJA-US Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a87d8ccc941480</t>
+          <t>https://www.indeed.com/viewjob?jk=4c121478651fef59</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Applications &amp; Data Analyst</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>The Community Foundation for Greater Atlanta</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Cloud Storage, Scala, Power BI, Tableau, AKS</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c100e86a4b30b0</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa8366af2ac5a61</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sr Developer, Enterprise Applications</t>
+          <t>Sr. Data and Platform Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, PySpark, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7df0d2f19226e92</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b516dee5bebdf7</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr Developer, Enterprise Applications</t>
+          <t>Associate Cloud Data Engineer - EDW Team</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>G.E.H.A</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Lee's Summit, MO, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cfdfcbeb6f3aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=eda83b90519c1a63</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sr Functional Analyst with Data Connect / Integration</t>
+          <t>AI Data Engineer Intern - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd158f889951e37</t>
+          <t>https://www.indeed.com/viewjob?jk=1697413820124a26</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Software Application Developer, IV IT</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31f79172dd2cf72</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdece1225c2c990</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer IV – Claims</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91758534ce0e5b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=858fa984b328a939</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack</t>
+          <t>Cloud Software Engineer (Azure)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, GCP, Snowflake, dbt, CI/CD, GitHub Actions, Docker</t>
+          <t>Azure, Data Factory, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00f231ced225306d</t>
+          <t>https://www.indeed.com/viewjob?jk=67e15f97e5cb54f7</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Software Engineer III - Platform Engineer</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,17 +5841,402 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02f995067a8af808</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>DevOps Engineer, Level 3</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>FJA-US Inc.</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad4efa0feb82038a</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>DevOps Engineer, Level 3</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>FJA-US Inc.</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68a87d8ccc941480</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Senior Applications &amp; Data Analyst</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>The Community Foundation for Greater Atlanta</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Cloud Storage, Scala, Power BI, Tableau, AKS</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67c100e86a4b30b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Sr Developer, Enterprise Applications</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Pilot Flying J</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Orange, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7df0d2f19226e92</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Sr Developer, Enterprise Applications</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Pilot Flying J</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9cfdfcbeb6f3aa6</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Sr Functional Analyst with Data Connect / Integration</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afd158f889951e37</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Software Application Developer, IV IT</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Centurion Health</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a31f79172dd2cf72</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer IV – Claims</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>The Standard Insurance</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91758534ce0e5b1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Software Engineer, Full Stack</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Athena, RDS, GCP, Snowflake, dbt, CI/CD, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00f231ced225306d</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
           <t>AWS, RDS, Kafka, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=73912ee7f3217027</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf46e42976391c6a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-26.xlsx
+++ b/results/job_matches_2026-09-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Intern, IT Data Analytics (2027)</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hollister Incorporated</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f2045b50523bff</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7a1bd8af02f9dc</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ad36cd86055a44</t>
+          <t>https://www.indeed.com/viewjob?jk=aa6bfaadd5a59007</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer (Internal Tools &amp; Platform)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224df3f1a9ee79b8</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0c40611e6f1095</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7055be6d8f9a7387</t>
+          <t>https://www.indeed.com/viewjob?jk=b557a1c3d0e30a4a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d8c98cbbde5e5</t>
+          <t>https://www.indeed.com/viewjob?jk=221dce02ae4400cf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer, Data - FreeWheel</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf28aa480065b669</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2dcbf84370ecd2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>TWFG Insurance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Dataflow, Spark, PySpark, Scala, Fact Tables</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944cc70dff5af5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc6da2f4c063d5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa6bfaadd5a59007</t>
+          <t>https://www.indeed.com/viewjob?jk=0f682845a41118d4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Internal Tools &amp; Platform)</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0c40611e6f1095</t>
+          <t>https://www.indeed.com/viewjob?jk=d67a70dfbcdb3cc3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b557a1c3d0e30a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=6f816dbfdf0d99a1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Data Engineer II (School of Medicine)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221dce02ae4400cf</t>
+          <t>https://www.indeed.com/viewjob?jk=379a8ad8bec448ca</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AFTERWORK</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>London, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462d1dfaba6a7d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d5d06d511ed0f968</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Data - FreeWheel</t>
+          <t>DevOps Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2dcbf84370ecd2</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae962c4658819a4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TWFG Insurance</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Dataflow, Spark, PySpark, Scala, Fact Tables</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc6da2f4c063d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6054cc97ae7070</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate Data Engineer, AI Data Products</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lincoln Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, Spark, Data Modeling, dbt</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326243a7df349c66</t>
+          <t>https://www.indeed.com/viewjob?jk=42e2ea145c1d3563</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be84cd3bc47c5004</t>
+          <t>https://www.indeed.com/viewjob?jk=49d99cd342cc792a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AWS Cloud</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f816dbfdf0d99a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8b8cf7db016ac733</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998cfb2b283317ea</t>
+          <t>https://www.indeed.com/viewjob?jk=b342fa1c8138648d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II (School of Medicine)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a8ad8bec448ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f78903bdefa25d5d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5d06d511ed0f968</t>
+          <t>https://www.indeed.com/viewjob?jk=72c9885d1791465d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML Infrastructure</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae962c4658819a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3e09f803e1046e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6054cc97ae7070</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5b8f3fa6f2af02</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131728c21bda1a28</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ae0bf58018f888</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e2ea145c1d3563</t>
+          <t>https://www.indeed.com/viewjob?jk=7dce389fccfb3534</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Engineer, Customer Store Experience</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d99cd342cc792a</t>
+          <t>https://www.indeed.com/viewjob?jk=bab9f52b7b9fec24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>VMware VDI to AWS WorkSpaces Core Migration Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b8cf7db016ac733</t>
+          <t>https://www.indeed.com/viewjob?jk=78bd9b74a1882f4e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Information Technology Architect | (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>City of Atlanta</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b342fa1c8138648d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e657852ef5f740</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineering Associate</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78903bdefa25d5d</t>
+          <t>https://www.indeed.com/viewjob?jk=a45ecb961e115a14</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Sr. Analytics Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c9885d1791465d</t>
+          <t>https://www.indeed.com/viewjob?jk=945bd3fa6f051f40</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Java/Spring Boot Software Engineer/Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Aguadilla, PR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3e09f803e1046e</t>
+          <t>https://www.indeed.com/viewjob?jk=b9abe3f58667967b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Hive, Spark, Scala, NoSQL, Data Modeling, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5b8f3fa6f2af02</t>
+          <t>https://www.indeed.com/viewjob?jk=52509eca710cb0dc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Distinguished AI and Data Security Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ae0bf58018f888</t>
+          <t>https://www.indeed.com/viewjob?jk=8d3211f519b547f7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Senior Software Engineer (Platform Engineering)-Remote, USA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dce389fccfb3534</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ab6a43be12efda</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Engineer, Customer Store Experience</t>
+          <t>Senior AWS DevOps Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>KNS IT Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, DataOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab9f52b7b9fec24</t>
+          <t>https://www.indeed.com/viewjob?jk=55665d3cb959d92b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>VMware VDI to AWS WorkSpaces Core Migration Architect</t>
+          <t>Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bd9b74a1882f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=85eff740f1ceace8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Information Technology Architect | (Cloud Engineer)</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>City of Atlanta</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e657852ef5f740</t>
+          <t>https://www.indeed.com/viewjob?jk=a07d991630064dac</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineering Associate</t>
+          <t>Cloud Data Solutions Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45ecb961e115a14</t>
+          <t>https://www.indeed.com/viewjob?jk=a46b634577cae67c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Analytics Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Ezee Fiber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, PostgreSQL, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=945bd3fa6f051f40</t>
+          <t>https://www.indeed.com/viewjob?jk=14553b87b9e8856d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java/Spring Boot Software Engineer/Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>iDC Logistics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Aguadilla, PR, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9abe3f58667967b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f033dfebaee3ca</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Sr. Associate Data Engineer, AI Data Products</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Scala, NoSQL, Data Modeling, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Glue, Lambda, Athena, API Gateway, ECS, IAM, RDS, dbt, MLOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52509eca710cb0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=63821a0502f55779</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
+          <t>Associate Actuary II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07bb0961c751f3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfc7194d4a210ff</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Distinguished AI and Data Security Engineer</t>
+          <t>Business Intelligence Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d3211f519b547f7</t>
+          <t>https://www.indeed.com/viewjob?jk=13861c16b28c1ecd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Senior DevOps Engineer - Matterport</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f2dbc076e5d856</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbdfdc99e931506</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6929f0e8b0d467e</t>
+          <t>https://www.indeed.com/viewjob?jk=ddff3d8fcac07d3a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55bf5e8aa6a1b00</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1b607fdff26a44</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full-stack Engineer 5 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b85bc0bda01150</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e33ea940cfabaf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a187bc45f903c25</t>
+          <t>https://www.indeed.com/viewjob?jk=c52f54f8e5be210c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ea3b4e869f0b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=bca244a4074f26cb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full Stack Engineer - 4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c766c5fed70eb0a</t>
+          <t>https://www.indeed.com/viewjob?jk=4acbff2d0e6ba792</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bcda2cd30fd616</t>
+          <t>https://www.indeed.com/viewjob?jk=a726f18ef6bec68d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638ef8567418dc48</t>
+          <t>https://www.indeed.com/viewjob?jk=9360083577d366e1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1a136d608291b</t>
+          <t>https://www.indeed.com/viewjob?jk=26af012597a937ac</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS, API, UI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd00710707d78e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0a471487d6e7ce5e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full Stack Engineer 4 (Bank Tech)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442e1899472aaaca</t>
+          <t>https://www.indeed.com/viewjob?jk=206971bfe0c7648e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17caa029de510739</t>
+          <t>https://www.indeed.com/viewjob?jk=f700dc035e701b44</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42aa0c7cd36d006a</t>
+          <t>https://www.indeed.com/viewjob?jk=cbde946ea5f19114</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full-stack Engineer 4 (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab6925d775e203f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f21d9e3e95a919b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5653e98fb8135f3</t>
+          <t>https://www.indeed.com/viewjob?jk=befbf1e1c644225d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=687232035e68a0a9</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc7880b49c1e317</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ba9f5f8c57b5360</t>
+          <t>https://www.indeed.com/viewjob?jk=38ecde40997dfe59</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Agentic Data Engineer, IC2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ClassLink, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7126e5851d589397</t>
+          <t>https://www.indeed.com/viewjob?jk=2a242ddcff013ad3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77cfd4f7c6e8001</t>
+          <t>https://www.indeed.com/viewjob?jk=4c121478651fef59</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59304446412e07c</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa8366af2ac5a61</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Sr. Data and Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, PySpark, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b64c007a0de94064</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b516dee5bebdf7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Associate Cloud Data Engineer - EDW Team</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>G.E.H.A</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lee's Summit, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,102 +3366,102 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86388f3c259eeff8</t>
+          <t>https://www.indeed.com/viewjob?jk=eda83b90519c1a63</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675f32b4ffa9a13</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdece1225c2c990</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034638488092da65</t>
+          <t>https://www.indeed.com/viewjob?jk=858fa984b328a939</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Cloud Software Engineer (Azure)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Azure, Data Factory, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,137 +3471,137 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac28966ddf697160</t>
+          <t>https://www.indeed.com/viewjob?jk=67e15f97e5cb54f7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24729823d8955c30</t>
+          <t>https://www.indeed.com/viewjob?jk=02f995067a8af808</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87a502c5ba52e486</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4efa0feb82038a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a20461db3b55f8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=68a87d8ccc941480</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Senior Applications &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Community Foundation for Greater Atlanta</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Cloud Storage, Scala, Power BI, Tableau, AKS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c63497e49a35949</t>
+          <t>https://www.indeed.com/viewjob?jk=67c100e86a4b30b0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Sr Developer, Enterprise Applications</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6deed82147b3397a</t>
+          <t>https://www.indeed.com/viewjob?jk=b7df0d2f19226e92</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Sr Developer, Enterprise Applications</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ab915125e1142b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cfdfcbeb6f3aa6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Software Application Developer, IV IT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e19c0167b5b707</t>
+          <t>https://www.indeed.com/viewjob?jk=a31f79172dd2cf72</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full-Stack Software Engineer IV – Claims</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3957c8134eb5449d</t>
+          <t>https://www.indeed.com/viewjob?jk=91758534ce0e5b1f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, EMR, Athena, RDS, GCP, Snowflake, dbt, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131fbd30ebce4b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=00f231ced225306d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Software Engineer III - Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Kafka, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc69f1717479209</t>
+          <t>https://www.indeed.com/viewjob?jk=73912ee7f3217027</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Full-stack Engineer 4 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3855,2386 +3855,6 @@
         </is>
       </c>
       <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbd490415ec98b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior STIBO Software Developer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Dover, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de9da7e405560c98</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior STIBO Software Developer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Bismarck, ND, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d443ab17a64dc4a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior STIBO Software Developer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abe9a8ea39da933e</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior STIBO Software Developer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2436088e04cb9418</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior STIBO Software Developer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4760b3a15e7c28bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior STIBO Software Developer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a34bf218fa3ecdb</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior STIBO Software Developer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Albany, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c29c8279e212129</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior STIBO Software Developer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Lansing, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbc6b68160b7f80</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior STIBO Software Developer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e67361e9400bbca3</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior STIBO Software Developer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56277a5a14ecfae3</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior STIBO Software Developer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Carson City, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64341d28e22d4d4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior STIBO Software Developer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Concord, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0db3535ef241d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Platform Engineering)-Remote, USA</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Tempus</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, MySQL</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ab6a43be12efda</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior AWS DevOps Architect</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>KNS IT Group</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, DataOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55665d3cb959d92b</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Software Engineer - Hybrid</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Mindex</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85eff740f1ceace8</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Software Engineer Associate III - Databricks</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a07d991630064dac</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Cloud Data Solutions Engineer - Financial Services</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a46b634577cae67c</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 - Kiewit Technology Group</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Kiewit Corporation</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69fd302298183375</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Sentara</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Norfolk, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0364757c79beba</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>vertage</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala, ETL</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d893afa2af62f4a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior GCP Data Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>vertage</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1919471b72d0ae9</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Ezee Fiber</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, PostgreSQL, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14553b87b9e8856d</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Associate Actuary II</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Wildfire Defense Systems</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfc7194d4a210ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer II - REMOTE</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Net Health</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13861c16b28c1ecd</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Sr. Associate Data Engineer, AI Data Products</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Lincoln Financial</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Radnor, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, API Gateway, ECS, IAM, RDS, dbt, MLOps</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63821a0502f55779</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>iDC Logistics</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>City of Industry, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, dbt</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f033dfebaee3ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Wausau, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8593692b74910cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer - Matterport</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>CoStar Group</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbdfdc99e931506</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Nelnet</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddff3d8fcac07d3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e33ea940cfabaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c52f54f8e5be210c</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bca244a4074f26cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer - 4</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4acbff2d0e6ba792</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a726f18ef6bec68d</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9360083577d366e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26af012597a937ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Full-Stack Engineer 4 (Python, Java, AWS, API, UI) (Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a471487d6e7ce5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4 (Bank Tech)</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=206971bfe0c7648e</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f700dc035e701b44</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbde946ea5f19114</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Remote-Eligible)</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f21d9e3e95a919b</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=befbf1e1c644225d</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Analytics Engineer (Power BI)</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Orion180 Insurance Services, LLC</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d65655a9bdf8af8</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc7880b49c1e317</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Big Data Architect</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38ecde40997dfe59</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2b3596f51501b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70480a7733a24dbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Agentic Data Engineer, IC2</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>ClassLink, Inc.</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a242ddcff013ad3</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Hanover, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c121478651fef59</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa8366af2ac5a61</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Sr. Data and Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, PySpark, ELT, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b516dee5bebdf7</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Associate Cloud Data Engineer - EDW Team</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>G.E.H.A</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Lee's Summit, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eda83b90519c1a63</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>AI Data Engineer Intern - QuantumBlack, AI by McKinsey</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>McKinsey &amp; Company</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt, Git, Python</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1697413820124a26</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Vital Services</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Allen, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdece1225c2c990</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Vital Services</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Oak Ridge, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=858fa984b328a939</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Cloud Software Engineer (Azure)</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67e15f97e5cb54f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>DevOps Engineer, Level 3</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>FJA-US Inc.</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02f995067a8af808</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>DevOps Engineer, Level 3</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>FJA-US Inc.</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4efa0feb82038a</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>DevOps Engineer, Level 3</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>FJA-US Inc.</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68a87d8ccc941480</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Senior Applications &amp; Data Analyst</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>The Community Foundation for Greater Atlanta</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Cloud Storage, Scala, Power BI, Tableau, AKS</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67c100e86a4b30b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Sr Developer, Enterprise Applications</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Pilot Flying J</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Orange, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b7df0d2f19226e92</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Sr Developer, Enterprise Applications</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Pilot Flying J</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cfdfcbeb6f3aa6</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Sr Functional Analyst with Data Connect / Integration</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afd158f889951e37</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Software Application Developer, IV IT</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a31f79172dd2cf72</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Engineer IV – Claims</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>The Standard Insurance</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91758534ce0e5b1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Software Engineer, Full Stack</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Athena, RDS, GCP, Snowflake, dbt, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00f231ced225306d</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73912ee7f3217027</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bf46e42976391c6a</t>
         </is>

--- a/results/job_matches_2026-09-26.xlsx
+++ b/results/job_matches_2026-09-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,95 +783,95 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5929a259b13da0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7a1bd8af02f9dc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Sr Data Engineer, AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, GCP, Spark, PySpark, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7a1bd8af02f9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=05fc81fdc3c7e4c8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data - Medical Cost Grouper - Remote</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Bronco Wine Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ceres, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, HBase, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Star Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ee7d4f1fc05ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=5e558da34cfe637e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, AI</t>
+          <t>DevSecOps</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Steerbridge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, GCP, Spark, PySpark, SQL Server</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Azure, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05fc81fdc3c7e4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=c41e154e6981a638</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>DWBI Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bronco Wine Company</t>
+          <t>Jersey Mike's</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ceres, CA, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Star Schema, Fact Tables</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e558da34cfe637e</t>
+          <t>https://www.indeed.com/viewjob?jk=03f2e368fab4382a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevSecOps</t>
+          <t>Full Stack Software Engineer, Integrity</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Steerbridge</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Azure, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c41e154e6981a638</t>
+          <t>https://www.indeed.com/viewjob?jk=836233526c2bfe4c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DWBI Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jersey Mike's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f2e368fab4382a</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef89900c1dc8244</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Integrity</t>
+          <t>Analytics Engineer, Integrity</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Dimensional Modeling, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836233526c2bfe4c</t>
+          <t>https://www.indeed.com/viewjob?jk=986e0cd967904817</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1077,38 +1077,38 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef89900c1dc8244</t>
+          <t>https://www.indeed.com/viewjob?jk=aa6bfaadd5a59007</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Integrity</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Dimensional Modeling, ELT, dbt, MLOps</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986e0cd967904817</t>
+          <t>https://www.indeed.com/viewjob?jk=b557a1c3d0e30a4a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa6bfaadd5a59007</t>
+          <t>https://www.indeed.com/viewjob?jk=221dce02ae4400cf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Internal Tools &amp; Platform)</t>
+          <t>Site Reliability Engineer, Data - FreeWheel</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0c40611e6f1095</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2dcbf84370ecd2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b557a1c3d0e30a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f682845a41118d4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221dce02ae4400cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d67a70dfbcdb3cc3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Data - FreeWheel</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2dcbf84370ecd2</t>
+          <t>https://www.indeed.com/viewjob?jk=6f816dbfdf0d99a1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II (School of Medicine)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TWFG Insurance</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Dataflow, Spark, PySpark, Scala, Fact Tables</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,102 +1336,102 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc6da2f4c063d5</t>
+          <t>https://www.indeed.com/viewjob?jk=379a8ad8bec448ca</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AWS Cloud</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f682845a41118d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5d06d511ed0f968</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AWS Cloud</t>
+          <t>DevOps Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67a70dfbcdb3cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae962c4658819a4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AWS Cloud</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f816dbfdf0d99a1</t>
+          <t>https://www.indeed.com/viewjob?jk=42e2ea145c1d3563</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer II (School of Medicine)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a8ad8bec448ca</t>
+          <t>https://www.indeed.com/viewjob?jk=49d99cd342cc792a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5d06d511ed0f968</t>
+          <t>https://www.indeed.com/viewjob?jk=8b8cf7db016ac733</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML Infrastructure</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae962c4658819a4</t>
+          <t>https://www.indeed.com/viewjob?jk=b342fa1c8138648d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6054cc97ae7070</t>
+          <t>https://www.indeed.com/viewjob?jk=f78903bdefa25d5d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e2ea145c1d3563</t>
+          <t>https://www.indeed.com/viewjob?jk=72c9885d1791465d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d99cd342cc792a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3e09f803e1046e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b8cf7db016ac733</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5b8f3fa6f2af02</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b342fa1c8138648d</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ae0bf58018f888</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78903bdefa25d5d</t>
+          <t>https://www.indeed.com/viewjob?jk=7dce389fccfb3534</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Engineer, Customer Store Experience</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c9885d1791465d</t>
+          <t>https://www.indeed.com/viewjob?jk=bab9f52b7b9fec24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>VMware VDI to AWS WorkSpaces Core Migration Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3e09f803e1046e</t>
+          <t>https://www.indeed.com/viewjob?jk=78bd9b74a1882f4e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Information Technology Architect | (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>City of Atlanta</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5b8f3fa6f2af02</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e657852ef5f740</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. Analytics Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ae0bf58018f888</t>
+          <t>https://www.indeed.com/viewjob?jk=945bd3fa6f051f40</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Data Engineering Associate</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dce389fccfb3534</t>
+          <t>https://www.indeed.com/viewjob?jk=a45ecb961e115a14</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer, Customer Store Experience</t>
+          <t>Java/Spring Boot Software Engineer/Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Aguadilla, PR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab9f52b7b9fec24</t>
+          <t>https://www.indeed.com/viewjob?jk=b9abe3f58667967b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VMware VDI to AWS WorkSpaces Core Migration Architect</t>
+          <t>Distinguished AI and Data Security Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bd9b74a1882f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d3211f519b547f7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Information Technology Architect | (Cloud Engineer)</t>
+          <t>Senior Software Engineer (Platform Engineering)-Remote, USA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>City of Atlanta</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e657852ef5f740</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ab6a43be12efda</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineering Associate</t>
+          <t>Senior AWS DevOps Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>KNS IT Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, DataOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45ecb961e115a14</t>
+          <t>https://www.indeed.com/viewjob?jk=55665d3cb959d92b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Analytics Analyst</t>
+          <t>Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=945bd3fa6f051f40</t>
+          <t>https://www.indeed.com/viewjob?jk=85eff740f1ceace8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java/Spring Boot Software Engineer/Developer</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Aguadilla, PR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9abe3f58667967b</t>
+          <t>https://www.indeed.com/viewjob?jk=a07d991630064dac</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Cloud Data Solutions Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Scala, NoSQL, Data Modeling, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52509eca710cb0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=a46b634577cae67c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Distinguished AI and Data Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Ezee Fiber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, PostgreSQL, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d3211f519b547f7</t>
+          <t>https://www.indeed.com/viewjob?jk=14553b87b9e8856d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Engineering)-Remote, USA</t>
+          <t>Sr. Associate Data Engineer, AI Data Products</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, API Gateway, ECS, IAM, RDS, dbt, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ab6a43be12efda</t>
+          <t>https://www.indeed.com/viewjob?jk=63821a0502f55779</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Architect</t>
+          <t>Business Intelligence Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KNS IT Group</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, DataOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55665d3cb959d92b</t>
+          <t>https://www.indeed.com/viewjob?jk=13861c16b28c1ecd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid</t>
+          <t>Associate Actuary II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eff740f1ceace8</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfc7194d4a210ff</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07d991630064dac</t>
+          <t>https://www.indeed.com/viewjob?jk=ddff3d8fcac07d3a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer - Financial Services</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46b634577cae67c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1b607fdff26a44</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 5 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ezee Fiber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, PostgreSQL, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14553b87b9e8856d</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e33ea940cfabaf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>iDC Logistics</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f033dfebaee3ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c52f54f8e5be210c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Associate Data Engineer, AI Data Products</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lincoln Financial</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, API Gateway, ECS, IAM, RDS, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63821a0502f55779</t>
+          <t>https://www.indeed.com/viewjob?jk=bca244a4074f26cb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate Actuary II</t>
+          <t>Full Stack Engineer - 4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfc7194d4a210ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4acbff2d0e6ba792</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II - REMOTE</t>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13861c16b28c1ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=a726f18ef6bec68d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Matterport</t>
+          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbdfdc99e931506</t>
+          <t>https://www.indeed.com/viewjob?jk=9360083577d366e1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddff3d8fcac07d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=26af012597a937ac</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS, API, UI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2661,19 +2661,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1b607fdff26a44</t>
+          <t>https://www.indeed.com/viewjob?jk=0a471487d6e7ce5e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
+          <t>Full Stack Engineer 4 (Bank Tech)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e33ea940cfabaf</t>
+          <t>https://www.indeed.com/viewjob?jk=206971bfe0c7648e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52f54f8e5be210c</t>
+          <t>https://www.indeed.com/viewjob?jk=f700dc035e701b44</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca244a4074f26cb</t>
+          <t>https://www.indeed.com/viewjob?jk=cbde946ea5f19114</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - 4</t>
+          <t>Full-stack Engineer 4 (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acbff2d0e6ba792</t>
+          <t>https://www.indeed.com/viewjob?jk=3f21d9e3e95a919b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
+          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a726f18ef6bec68d</t>
+          <t>https://www.indeed.com/viewjob?jk=befbf1e1c644225d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,15 +2858,15 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9360083577d366e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc7880b49c1e317</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26af012597a937ac</t>
+          <t>https://www.indeed.com/viewjob?jk=38ecde40997dfe59</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, Java, AWS, API, UI) (Enterprise Platforms Technology)</t>
+          <t>Agentic Data Engineer, IC2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ClassLink, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a471487d6e7ce5e</t>
+          <t>https://www.indeed.com/viewjob?jk=2a242ddcff013ad3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Bank Tech)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=206971bfe0c7648e</t>
+          <t>https://www.indeed.com/viewjob?jk=4c121478651fef59</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f700dc035e701b44</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa8366af2ac5a61</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Sr. Data and Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, PySpark, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,94 +3051,94 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbde946ea5f19114</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b516dee5bebdf7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Remote-Eligible)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f21d9e3e95a919b</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdece1225c2c990</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=befbf1e1c644225d</t>
+          <t>https://www.indeed.com/viewjob?jk=858fa984b328a939</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Cloud Software Engineer (Azure)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+          <t>Azure, Data Factory, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc7880b49c1e317</t>
+          <t>https://www.indeed.com/viewjob?jk=67e15f97e5cb54f7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ecde40997dfe59</t>
+          <t>https://www.indeed.com/viewjob?jk=02f995067a8af808</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Agentic Data Engineer, IC2</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ClassLink, Inc.</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a242ddcff013ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4efa0feb82038a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c121478651fef59</t>
+          <t>https://www.indeed.com/viewjob?jk=68a87d8ccc941480</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Applications &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Community Foundation for Greater Atlanta</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Cloud Storage, Scala, Power BI, Tableau, AKS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa8366af2ac5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=67c100e86a4b30b0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Data and Platform Engineer</t>
+          <t>Software Application Developer, IV IT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, PySpark, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b516dee5bebdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=a31f79172dd2cf72</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer - EDW Team</t>
+          <t>Full-Stack Software Engineer IV – Claims</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>G.E.H.A</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lee's Summit, MO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda83b90519c1a63</t>
+          <t>https://www.indeed.com/viewjob?jk=91758534ce0e5b1f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Developer, Enterprise Applications</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdece1225c2c990</t>
+          <t>https://www.indeed.com/viewjob?jk=b7df0d2f19226e92</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Developer, Enterprise Applications</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858fa984b328a939</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cfdfcbeb6f3aa6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer (Azure)</t>
+          <t>Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, EMR, Athena, RDS, GCP, Snowflake, dbt, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67e15f97e5cb54f7</t>
+          <t>https://www.indeed.com/viewjob?jk=00f231ced225306d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Level 3</t>
+          <t>Software Engineer III - Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FJA-US Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Kafka, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f995067a8af808</t>
+          <t>https://www.indeed.com/viewjob?jk=73912ee7f3217027</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Level 3</t>
+          <t>Full-stack Engineer 4 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FJA-US Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,330 +3531,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4efa0feb82038a</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>DevOps Engineer, Level 3</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>FJA-US Inc.</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68a87d8ccc941480</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Applications &amp; Data Analyst</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>The Community Foundation for Greater Atlanta</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Cloud Storage, Scala, Power BI, Tableau, AKS</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67c100e86a4b30b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr Developer, Enterprise Applications</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Pilot Flying J</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Orange, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b7df0d2f19226e92</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Sr Developer, Enterprise Applications</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Pilot Flying J</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cfdfcbeb6f3aa6</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Software Application Developer, IV IT</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a31f79172dd2cf72</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Engineer IV – Claims</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>The Standard Insurance</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91758534ce0e5b1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Software Engineer, Full Stack</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Athena, RDS, GCP, Snowflake, dbt, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00f231ced225306d</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73912ee7f3217027</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bf46e42976391c6a</t>
         </is>

--- a/results/job_matches_2026-09-26.xlsx
+++ b/results/job_matches_2026-09-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer</t>
+          <t>Systems Engineer (TraCSS Mission Integration)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Everon</t>
+          <t>ASRC Federal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Suitland-Silver Hill, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bf341f814fc4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4229e45505a54081</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect</t>
+          <t>Full-stack Engineer 4 (Apache Spark and Java)( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=536f7d54c3314639</t>
+          <t>https://www.indeed.com/viewjob?jk=1c536a9bd99ef94e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Systems Engineer (TraCSS Mission Integration)</t>
+          <t>Full-stack Engineer 4 (Apache Spark and Java)( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ASRC Federal</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Suitland-Silver Hill, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4229e45505a54081</t>
+          <t>https://www.indeed.com/viewjob?jk=61acd17e8e4caf4c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Apache Spark and Java)( Enterprise Platforms Technology)</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,50 +723,50 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c536a9bd99ef94e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7a1bd8af02f9dc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Apache Spark and Java)( Enterprise Platforms Technology)</t>
+          <t>Sr Data Engineer, AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, GCP, Spark, PySpark, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61acd17e8e4caf4c</t>
+          <t>https://www.indeed.com/viewjob?jk=05fc81fdc3c7e4c8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bronco Wine Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ceres, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Star Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7a1bd8af02f9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5e558da34cfe637e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, AI</t>
+          <t>DevSecOps</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Steerbridge</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, GCP, Spark, PySpark, SQL Server</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Azure, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05fc81fdc3c7e4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=c41e154e6981a638</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>DWBI Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bronco Wine Company</t>
+          <t>Jersey Mike's</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ceres, CA, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Star Schema, Fact Tables</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e558da34cfe637e</t>
+          <t>https://www.indeed.com/viewjob?jk=03f2e368fab4382a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevSecOps</t>
+          <t>Full Stack Software Engineer, Integrity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Steerbridge</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Azure, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c41e154e6981a638</t>
+          <t>https://www.indeed.com/viewjob?jk=836233526c2bfe4c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DWBI Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jersey Mike's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f2e368fab4382a</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef89900c1dc8244</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Integrity</t>
+          <t>Analytics Engineer, Integrity</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Dimensional Modeling, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836233526c2bfe4c</t>
+          <t>https://www.indeed.com/viewjob?jk=986e0cd967904817</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1007,38 +1007,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef89900c1dc8244</t>
+          <t>https://www.indeed.com/viewjob?jk=aa6bfaadd5a59007</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Integrity</t>
+          <t>Site Reliability Engineer, Data - FreeWheel</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Dimensional Modeling, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986e0cd967904817</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2dcbf84370ecd2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa6bfaadd5a59007</t>
+          <t>https://www.indeed.com/viewjob?jk=0f682845a41118d4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b557a1c3d0e30a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=d67a70dfbcdb3cc3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,137 +1161,137 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221dce02ae4400cf</t>
+          <t>https://www.indeed.com/viewjob?jk=6f816dbfdf0d99a1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Data - FreeWheel</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2dcbf84370ecd2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d55a501fc68d234</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AWS Cloud</t>
+          <t>Data Engineer II (School of Medicine)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f682845a41118d4</t>
+          <t>https://www.indeed.com/viewjob?jk=379a8ad8bec448ca</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AWS Cloud</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67a70dfbcdb3cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=d5d06d511ed0f968</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AWS Cloud</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f816dbfdf0d99a1</t>
+          <t>https://www.indeed.com/viewjob?jk=42e2ea145c1d3563</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II (School of Medicine)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a8ad8bec448ca</t>
+          <t>https://www.indeed.com/viewjob?jk=49d99cd342cc792a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5d06d511ed0f968</t>
+          <t>https://www.indeed.com/viewjob?jk=8b8cf7db016ac733</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML Infrastructure</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae962c4658819a4</t>
+          <t>https://www.indeed.com/viewjob?jk=b342fa1c8138648d</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e2ea145c1d3563</t>
+          <t>https://www.indeed.com/viewjob?jk=f78903bdefa25d5d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d99cd342cc792a</t>
+          <t>https://www.indeed.com/viewjob?jk=72c9885d1791465d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b8cf7db016ac733</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3e09f803e1046e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b342fa1c8138648d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5b8f3fa6f2af02</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78903bdefa25d5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ae0bf58018f888</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c9885d1791465d</t>
+          <t>https://www.indeed.com/viewjob?jk=7dce389fccfb3534</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Engineer, Customer Store Experience</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3e09f803e1046e</t>
+          <t>https://www.indeed.com/viewjob?jk=bab9f52b7b9fec24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineering Associate</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5b8f3fa6f2af02</t>
+          <t>https://www.indeed.com/viewjob?jk=a45ecb961e115a14</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Java/Spring Boot Software Engineer/Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Aguadilla, PR, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ae0bf58018f888</t>
+          <t>https://www.indeed.com/viewjob?jk=b9abe3f58667967b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Distinguished AI and Data Security Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dce389fccfb3534</t>
+          <t>https://www.indeed.com/viewjob?jk=8d3211f519b547f7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer, Customer Store Experience</t>
+          <t>Senior Software Engineer (Platform Engineering)-Remote, USA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab9f52b7b9fec24</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ab6a43be12efda</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VMware VDI to AWS WorkSpaces Core Migration Architect</t>
+          <t>Senior AWS DevOps Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>KNS IT Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Scala, DataOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bd9b74a1882f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=55665d3cb959d92b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Information Technology Architect | (Cloud Engineer)</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>City of Atlanta</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e657852ef5f740</t>
+          <t>https://www.indeed.com/viewjob?jk=a07d991630064dac</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Analytics Analyst</t>
+          <t>Cloud Data Solutions Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=945bd3fa6f051f40</t>
+          <t>https://www.indeed.com/viewjob?jk=a46b634577cae67c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineering Associate</t>
+          <t>Associate Actuary II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45ecb961e115a14</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfc7194d4a210ff</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Java/Spring Boot Software Engineer/Developer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Aguadilla, PR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9abe3f58667967b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1b607fdff26a44</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Distinguished AI and Data Security Engineer</t>
+          <t>Full-stack Engineer 5 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d3211f519b547f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e33ea940cfabaf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Engineering)-Remote, USA</t>
+          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ab6a43be12efda</t>
+          <t>https://www.indeed.com/viewjob?jk=c52f54f8e5be210c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Architect</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KNS IT Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, DataOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55665d3cb959d92b</t>
+          <t>https://www.indeed.com/viewjob?jk=bca244a4074f26cb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid</t>
+          <t>Full Stack Engineer - 4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eff740f1ceace8</t>
+          <t>https://www.indeed.com/viewjob?jk=4acbff2d0e6ba792</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07d991630064dac</t>
+          <t>https://www.indeed.com/viewjob?jk=a726f18ef6bec68d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer - Financial Services</t>
+          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46b634577cae67c</t>
+          <t>https://www.indeed.com/viewjob?jk=9360083577d366e1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ezee Fiber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, PostgreSQL, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14553b87b9e8856d</t>
+          <t>https://www.indeed.com/viewjob?jk=26af012597a937ac</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Associate Data Engineer, AI Data Products</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS, API, UI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lincoln Financial</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, API Gateway, ECS, IAM, RDS, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63821a0502f55779</t>
+          <t>https://www.indeed.com/viewjob?jk=0a471487d6e7ce5e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II - REMOTE</t>
+          <t>Full Stack Engineer 4 (Bank Tech)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13861c16b28c1ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=206971bfe0c7648e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate Actuary II</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfc7194d4a210ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f700dc035e701b44</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddff3d8fcac07d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=cbde946ea5f19114</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2381,19 +2381,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1b607fdff26a44</t>
+          <t>https://www.indeed.com/viewjob?jk=3f21d9e3e95a919b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
+          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e33ea940cfabaf</t>
+          <t>https://www.indeed.com/viewjob?jk=befbf1e1c644225d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,15 +2438,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52f54f8e5be210c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc7880b49c1e317</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca244a4074f26cb</t>
+          <t>https://www.indeed.com/viewjob?jk=38ecde40997dfe59</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - 4</t>
+          <t>Agentic Data Engineer, IC2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ClassLink, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acbff2d0e6ba792</t>
+          <t>https://www.indeed.com/viewjob?jk=2a242ddcff013ad3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a726f18ef6bec68d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c121478651fef59</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9360083577d366e1</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa8366af2ac5a61</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Cloud Software Engineer (Azure)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,137 +2631,137 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26af012597a937ac</t>
+          <t>https://www.indeed.com/viewjob?jk=67e15f97e5cb54f7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, Java, AWS, API, UI) (Enterprise Platforms Technology)</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a471487d6e7ce5e</t>
+          <t>https://www.indeed.com/viewjob?jk=02f995067a8af808</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Bank Tech)</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=206971bfe0c7648e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4efa0feb82038a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f700dc035e701b44</t>
+          <t>https://www.indeed.com/viewjob?jk=68a87d8ccc941480</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior Applications &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Community Foundation for Greater Atlanta</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Cloud Storage, Scala, Power BI, Tableau, AKS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbde946ea5f19114</t>
+          <t>https://www.indeed.com/viewjob?jk=67c100e86a4b30b0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Remote-Eligible)</t>
+          <t>Software Application Developer, IV IT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f21d9e3e95a919b</t>
+          <t>https://www.indeed.com/viewjob?jk=a31f79172dd2cf72</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
+          <t>Full-Stack Software Engineer IV – Claims</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=befbf1e1c644225d</t>
+          <t>https://www.indeed.com/viewjob?jk=91758534ce0e5b1f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Sr Developer, Enterprise Applications</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc7880b49c1e317</t>
+          <t>https://www.indeed.com/viewjob?jk=b7df0d2f19226e92</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Sr Developer, Enterprise Applications</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ecde40997dfe59</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cfdfcbeb6f3aa6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Agentic Data Engineer, IC2</t>
+          <t>Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ClassLink, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Kubernetes, Git</t>
+          <t>AWS, EMR, Athena, RDS, GCP, Snowflake, dbt, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a242ddcff013ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=00f231ced225306d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c121478651fef59</t>
+          <t>https://www.indeed.com/viewjob?jk=bf46e42976391c6a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Engineer III - Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Kafka, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,532 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa8366af2ac5a61</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Sr. Data and Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, PySpark, ELT, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b516dee5bebdf7</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Vital Services</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Allen, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdece1225c2c990</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Vital Services</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Oak Ridge, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=858fa984b328a939</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Cloud Software Engineer (Azure)</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67e15f97e5cb54f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>DevOps Engineer, Level 3</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>FJA-US Inc.</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02f995067a8af808</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>DevOps Engineer, Level 3</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>FJA-US Inc.</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4efa0feb82038a</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>DevOps Engineer, Level 3</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>FJA-US Inc.</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68a87d8ccc941480</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Applications &amp; Data Analyst</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>The Community Foundation for Greater Atlanta</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Cloud Storage, Scala, Power BI, Tableau, AKS</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67c100e86a4b30b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Software Application Developer, IV IT</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a31f79172dd2cf72</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Engineer IV – Claims</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>The Standard Insurance</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91758534ce0e5b1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Sr Developer, Enterprise Applications</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Pilot Flying J</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Orange, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b7df0d2f19226e92</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Sr Developer, Enterprise Applications</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Pilot Flying J</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, SQL Server, PostgreSQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cfdfcbeb6f3aa6</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Software Engineer, Full Stack</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Athena, RDS, GCP, Snowflake, dbt, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00f231ced225306d</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=73912ee7f3217027</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf46e42976391c6a</t>
         </is>
       </c>
     </row>
